--- a/safety_inspection_forms/011_hazard_identification_checklist--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/011_hazard_identification_checklist--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_a',_'value':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'category_a', 'value': 'category_a'}</t>
+          <t>category a</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_b',_'value':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'category_b', 'value': 'category_b'}</t>
+          <t>category b</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'category_c',_'value':_'category_c'}</t>
+          <t>category_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'category_c', 'value': 'category_c'}</t>
+          <t>category c</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'frequent',_'value':_'frequent'}</t>
+          <t>frequent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'frequent', 'value': 'frequent'}</t>
+          <t>frequent</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'occasional',_'value':_'occasional'}</t>
+          <t>occasional</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'occasional', 'value': 'occasional'}</t>
+          <t>occasional</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rare',_'value':_'rare'}</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'rare', 'value': 'rare'}</t>
+          <t>rare</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'low', 'value': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium', 'value': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'high', 'value': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
